--- a/شركة الشرق العربي للتامين.xlsx
+++ b/شركة الشرق العربي للتامين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2218177-6DEC-4C9C-8C8F-832114557FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436D2EE8-DD14-4808-A87A-4A78D30422F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="407">
   <si>
     <t>الرقم</t>
   </si>
@@ -1215,6 +1215,45 @@
   </si>
   <si>
     <t>يحيى الشماسين</t>
+  </si>
+  <si>
+    <t>نزار شاكر مصطفى</t>
+  </si>
+  <si>
+    <t>انتصار عامر السعيدات</t>
+  </si>
+  <si>
+    <t>ايمان هارون موسى الحسنات</t>
+  </si>
+  <si>
+    <t>حنان احمد الفلحات</t>
+  </si>
+  <si>
+    <t>كندا عامر السعيدات</t>
+  </si>
+  <si>
+    <t>ليان يحيى الشماسين</t>
+  </si>
+  <si>
+    <t>محمد سعيد ابوبكر</t>
+  </si>
+  <si>
+    <t>دانا يحيى الشماسين</t>
+  </si>
+  <si>
+    <t>محمد العمرات</t>
+  </si>
+  <si>
+    <t>حسام الهاشم</t>
+  </si>
+  <si>
+    <t>عبدالله حسن الطيب</t>
+  </si>
+  <si>
+    <t>اليمامه ناصر الشماسين</t>
+  </si>
+  <si>
+    <t>ساجده علي العمرات</t>
   </si>
 </sst>
 </file>
@@ -1274,12 +1313,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor auto="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1309,7 +1354,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1329,6 +1374,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1629,8 +1678,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:N676" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N676" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:N715" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N715" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N676">
     <sortCondition ref="F1:F676"/>
   </sortState>
@@ -1975,7 +2024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N676"/>
+  <dimension ref="A1:N715"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -31179,6 +31228,1566 @@
       <c r="M676" s="5"/>
       <c r="N676" s="5"/>
     </row>
+    <row r="677" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A677" s="11">
+        <v>1</v>
+      </c>
+      <c r="B677" s="11">
+        <v>2011668</v>
+      </c>
+      <c r="C677" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="D677" s="11">
+        <v>88321324</v>
+      </c>
+      <c r="E677" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F677" s="12">
+        <v>46207</v>
+      </c>
+      <c r="G677" s="13">
+        <v>36.49</v>
+      </c>
+      <c r="H677" s="13">
+        <v>7.298</v>
+      </c>
+      <c r="I677" s="13">
+        <v>29.192</v>
+      </c>
+      <c r="J677" s="14">
+        <f t="shared" ref="J677:J708" si="22">G677*0.94-H677</f>
+        <v>27.002600000000001</v>
+      </c>
+      <c r="K677" s="14"/>
+      <c r="L677" s="14">
+        <f t="shared" ref="L677:L708" si="23">J677-K677</f>
+        <v>27.002600000000001</v>
+      </c>
+      <c r="M677" s="14"/>
+      <c r="N677" s="14"/>
+    </row>
+    <row r="678" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A678" s="11">
+        <v>2</v>
+      </c>
+      <c r="B678" s="11">
+        <v>2011647</v>
+      </c>
+      <c r="C678" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D678" s="11">
+        <v>88321287</v>
+      </c>
+      <c r="E678" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F678" s="12">
+        <v>46210</v>
+      </c>
+      <c r="G678" s="13">
+        <v>41.51</v>
+      </c>
+      <c r="H678" s="13">
+        <v>8.3019999999999996</v>
+      </c>
+      <c r="I678" s="13">
+        <v>33.207999999999998</v>
+      </c>
+      <c r="J678" s="14">
+        <f t="shared" si="22"/>
+        <v>30.717399999999998</v>
+      </c>
+      <c r="K678" s="14"/>
+      <c r="L678" s="14">
+        <f t="shared" si="23"/>
+        <v>30.717399999999998</v>
+      </c>
+      <c r="M678" s="14"/>
+      <c r="N678" s="14"/>
+    </row>
+    <row r="679" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A679" s="11">
+        <v>3</v>
+      </c>
+      <c r="B679" s="11">
+        <v>2011648</v>
+      </c>
+      <c r="C679" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="D679" s="11">
+        <v>88321289</v>
+      </c>
+      <c r="E679" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F679" s="12">
+        <v>46210</v>
+      </c>
+      <c r="G679" s="13">
+        <v>42.92</v>
+      </c>
+      <c r="H679" s="13">
+        <v>8.5839999999999996</v>
+      </c>
+      <c r="I679" s="13">
+        <v>34.335999999999999</v>
+      </c>
+      <c r="J679" s="14">
+        <f t="shared" si="22"/>
+        <v>31.7608</v>
+      </c>
+      <c r="K679" s="14"/>
+      <c r="L679" s="14">
+        <f t="shared" si="23"/>
+        <v>31.7608</v>
+      </c>
+      <c r="M679" s="14"/>
+      <c r="N679" s="14"/>
+    </row>
+    <row r="680" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A680" s="11">
+        <v>4</v>
+      </c>
+      <c r="B680" s="11">
+        <v>2064762</v>
+      </c>
+      <c r="C680" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D680" s="11">
+        <v>90789657</v>
+      </c>
+      <c r="E680" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F680" s="12">
+        <v>46213</v>
+      </c>
+      <c r="G680" s="13">
+        <v>16.39</v>
+      </c>
+      <c r="H680" s="13">
+        <v>2.4580000000000002</v>
+      </c>
+      <c r="I680" s="13">
+        <v>13.932</v>
+      </c>
+      <c r="J680" s="14">
+        <f t="shared" si="22"/>
+        <v>12.948599999999999</v>
+      </c>
+      <c r="K680" s="14"/>
+      <c r="L680" s="14">
+        <f t="shared" si="23"/>
+        <v>12.948599999999999</v>
+      </c>
+      <c r="M680" s="14"/>
+      <c r="N680" s="14"/>
+    </row>
+    <row r="681" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A681" s="11">
+        <v>5</v>
+      </c>
+      <c r="B681" s="11">
+        <v>2064887</v>
+      </c>
+      <c r="C681" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D681" s="11">
+        <v>90790629</v>
+      </c>
+      <c r="E681" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F681" s="12">
+        <v>46213</v>
+      </c>
+      <c r="G681" s="13">
+        <v>9.26</v>
+      </c>
+      <c r="H681" s="13">
+        <v>1.389</v>
+      </c>
+      <c r="I681" s="13">
+        <v>7.8710000000000004</v>
+      </c>
+      <c r="J681" s="14">
+        <f t="shared" si="22"/>
+        <v>7.3153999999999995</v>
+      </c>
+      <c r="K681" s="14"/>
+      <c r="L681" s="14">
+        <f t="shared" si="23"/>
+        <v>7.3153999999999995</v>
+      </c>
+      <c r="M681" s="14"/>
+      <c r="N681" s="14"/>
+    </row>
+    <row r="682" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A682" s="11">
+        <v>6</v>
+      </c>
+      <c r="B682" s="11">
+        <v>2011677</v>
+      </c>
+      <c r="C682" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D682" s="11">
+        <v>88321527</v>
+      </c>
+      <c r="E682" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F682" s="12">
+        <v>46214</v>
+      </c>
+      <c r="G682" s="13">
+        <v>44.73</v>
+      </c>
+      <c r="H682" s="13">
+        <v>8.9459999999999997</v>
+      </c>
+      <c r="I682" s="13">
+        <v>35.783999999999999</v>
+      </c>
+      <c r="J682" s="14">
+        <f t="shared" si="22"/>
+        <v>33.100199999999994</v>
+      </c>
+      <c r="K682" s="14"/>
+      <c r="L682" s="14">
+        <f t="shared" si="23"/>
+        <v>33.100199999999994</v>
+      </c>
+      <c r="M682" s="14"/>
+      <c r="N682" s="14"/>
+    </row>
+    <row r="683" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A683" s="11">
+        <v>7</v>
+      </c>
+      <c r="B683" s="11">
+        <v>1988556</v>
+      </c>
+      <c r="C683" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="D683" s="11">
+        <v>90784277</v>
+      </c>
+      <c r="E683" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F683" s="12">
+        <v>46215</v>
+      </c>
+      <c r="G683" s="13">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="H683" s="13">
+        <v>4.819</v>
+      </c>
+      <c r="I683" s="13">
+        <v>27.311</v>
+      </c>
+      <c r="J683" s="14">
+        <f t="shared" si="22"/>
+        <v>25.383200000000002</v>
+      </c>
+      <c r="K683" s="14"/>
+      <c r="L683" s="14">
+        <f t="shared" si="23"/>
+        <v>25.383200000000002</v>
+      </c>
+      <c r="M683" s="14"/>
+      <c r="N683" s="14"/>
+    </row>
+    <row r="684" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A684" s="11">
+        <v>8</v>
+      </c>
+      <c r="B684" s="11">
+        <v>1988557</v>
+      </c>
+      <c r="C684" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="D684" s="11">
+        <v>90784266</v>
+      </c>
+      <c r="E684" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F684" s="12">
+        <v>46215</v>
+      </c>
+      <c r="G684" s="13">
+        <v>48.96</v>
+      </c>
+      <c r="H684" s="13">
+        <v>7.3440000000000003</v>
+      </c>
+      <c r="I684" s="13">
+        <v>41.616</v>
+      </c>
+      <c r="J684" s="14">
+        <f t="shared" si="22"/>
+        <v>38.678399999999996</v>
+      </c>
+      <c r="K684" s="14"/>
+      <c r="L684" s="14">
+        <f t="shared" si="23"/>
+        <v>38.678399999999996</v>
+      </c>
+      <c r="M684" s="14"/>
+      <c r="N684" s="14"/>
+    </row>
+    <row r="685" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A685" s="11">
+        <v>9</v>
+      </c>
+      <c r="B685" s="11">
+        <v>1988658</v>
+      </c>
+      <c r="C685" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D685" s="11">
+        <v>90784350</v>
+      </c>
+      <c r="E685" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F685" s="12">
+        <v>46216</v>
+      </c>
+      <c r="G685" s="13">
+        <v>7.98</v>
+      </c>
+      <c r="H685" s="13">
+        <v>1.1970000000000001</v>
+      </c>
+      <c r="I685" s="13">
+        <v>6.7830000000000004</v>
+      </c>
+      <c r="J685" s="14">
+        <f t="shared" si="22"/>
+        <v>6.3041999999999998</v>
+      </c>
+      <c r="K685" s="14"/>
+      <c r="L685" s="14">
+        <f t="shared" si="23"/>
+        <v>6.3041999999999998</v>
+      </c>
+      <c r="M685" s="14"/>
+      <c r="N685" s="14"/>
+    </row>
+    <row r="686" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A686" s="11">
+        <v>10</v>
+      </c>
+      <c r="B686" s="11">
+        <v>2065065</v>
+      </c>
+      <c r="C686" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="D686" s="11">
+        <v>90787841</v>
+      </c>
+      <c r="E686" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F686" s="12">
+        <v>46216</v>
+      </c>
+      <c r="G686" s="13">
+        <v>66.98</v>
+      </c>
+      <c r="H686" s="13">
+        <v>10.047000000000001</v>
+      </c>
+      <c r="I686" s="13">
+        <v>56.933</v>
+      </c>
+      <c r="J686" s="14">
+        <f t="shared" si="22"/>
+        <v>52.914199999999994</v>
+      </c>
+      <c r="K686" s="14"/>
+      <c r="L686" s="14">
+        <f t="shared" si="23"/>
+        <v>52.914199999999994</v>
+      </c>
+      <c r="M686" s="14"/>
+      <c r="N686" s="14"/>
+    </row>
+    <row r="687" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A687" s="11">
+        <v>11</v>
+      </c>
+      <c r="B687" s="11">
+        <v>2065068</v>
+      </c>
+      <c r="C687" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D687" s="11">
+        <v>90787847</v>
+      </c>
+      <c r="E687" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F687" s="12">
+        <v>46216</v>
+      </c>
+      <c r="G687" s="13">
+        <v>69.34</v>
+      </c>
+      <c r="H687" s="13">
+        <v>10.401</v>
+      </c>
+      <c r="I687" s="13">
+        <v>58.939</v>
+      </c>
+      <c r="J687" s="14">
+        <f t="shared" si="22"/>
+        <v>54.778599999999997</v>
+      </c>
+      <c r="K687" s="14"/>
+      <c r="L687" s="14">
+        <f t="shared" si="23"/>
+        <v>54.778599999999997</v>
+      </c>
+      <c r="M687" s="14"/>
+      <c r="N687" s="14"/>
+    </row>
+    <row r="688" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A688" s="11">
+        <v>12</v>
+      </c>
+      <c r="B688" s="11">
+        <v>1849233</v>
+      </c>
+      <c r="C688" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="D688" s="11">
+        <v>90828800</v>
+      </c>
+      <c r="E688" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F688" s="12">
+        <v>46218</v>
+      </c>
+      <c r="G688" s="13">
+        <v>44.55</v>
+      </c>
+      <c r="H688" s="13">
+        <v>8.91</v>
+      </c>
+      <c r="I688" s="13">
+        <v>35.64</v>
+      </c>
+      <c r="J688" s="14">
+        <f t="shared" si="22"/>
+        <v>32.966999999999999</v>
+      </c>
+      <c r="K688" s="14"/>
+      <c r="L688" s="14">
+        <f t="shared" si="23"/>
+        <v>32.966999999999999</v>
+      </c>
+      <c r="M688" s="14"/>
+      <c r="N688" s="14"/>
+    </row>
+    <row r="689" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A689" s="11">
+        <v>13</v>
+      </c>
+      <c r="B689" s="11">
+        <v>2033729</v>
+      </c>
+      <c r="C689" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="D689" s="11">
+        <v>90784518</v>
+      </c>
+      <c r="E689" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F689" s="12">
+        <v>46219</v>
+      </c>
+      <c r="G689" s="13">
+        <v>83.32</v>
+      </c>
+      <c r="H689" s="13">
+        <v>12.497999999999999</v>
+      </c>
+      <c r="I689" s="13">
+        <v>70.822000000000003</v>
+      </c>
+      <c r="J689" s="14">
+        <f t="shared" si="22"/>
+        <v>65.822799999999987</v>
+      </c>
+      <c r="K689" s="14"/>
+      <c r="L689" s="14">
+        <f t="shared" si="23"/>
+        <v>65.822799999999987</v>
+      </c>
+      <c r="M689" s="14"/>
+      <c r="N689" s="14"/>
+    </row>
+    <row r="690" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A690" s="11">
+        <v>14</v>
+      </c>
+      <c r="B690" s="11">
+        <v>1876018</v>
+      </c>
+      <c r="C690" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D690" s="11">
+        <v>88579641</v>
+      </c>
+      <c r="E690" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F690" s="12">
+        <v>46221</v>
+      </c>
+      <c r="G690" s="13">
+        <v>69.930000000000007</v>
+      </c>
+      <c r="H690" s="13">
+        <v>13.986000000000001</v>
+      </c>
+      <c r="I690" s="13">
+        <v>55.944000000000003</v>
+      </c>
+      <c r="J690" s="14">
+        <f t="shared" si="22"/>
+        <v>51.748199999999997</v>
+      </c>
+      <c r="K690" s="14"/>
+      <c r="L690" s="14">
+        <f t="shared" si="23"/>
+        <v>51.748199999999997</v>
+      </c>
+      <c r="M690" s="14"/>
+      <c r="N690" s="14"/>
+    </row>
+    <row r="691" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A691" s="11">
+        <v>15</v>
+      </c>
+      <c r="B691" s="11">
+        <v>1988680</v>
+      </c>
+      <c r="C691" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D691" s="11">
+        <v>90786063</v>
+      </c>
+      <c r="E691" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F691" s="12">
+        <v>46221</v>
+      </c>
+      <c r="G691" s="13">
+        <v>47.38</v>
+      </c>
+      <c r="H691" s="13">
+        <v>7.1070000000000002</v>
+      </c>
+      <c r="I691" s="13">
+        <v>40.273000000000003</v>
+      </c>
+      <c r="J691" s="14">
+        <f t="shared" si="22"/>
+        <v>37.430199999999999</v>
+      </c>
+      <c r="K691" s="14"/>
+      <c r="L691" s="14">
+        <f t="shared" si="23"/>
+        <v>37.430199999999999</v>
+      </c>
+      <c r="M691" s="14"/>
+      <c r="N691" s="14"/>
+    </row>
+    <row r="692" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A692" s="11">
+        <v>16</v>
+      </c>
+      <c r="B692" s="11">
+        <v>2011610</v>
+      </c>
+      <c r="C692" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D692" s="11">
+        <v>88321242</v>
+      </c>
+      <c r="E692" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F692" s="12">
+        <v>46221</v>
+      </c>
+      <c r="G692" s="13">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="H692" s="13">
+        <v>7.76</v>
+      </c>
+      <c r="I692" s="13">
+        <v>31.04</v>
+      </c>
+      <c r="J692" s="14">
+        <f t="shared" si="22"/>
+        <v>28.711999999999996</v>
+      </c>
+      <c r="K692" s="14"/>
+      <c r="L692" s="14">
+        <f t="shared" si="23"/>
+        <v>28.711999999999996</v>
+      </c>
+      <c r="M692" s="14"/>
+      <c r="N692" s="14"/>
+    </row>
+    <row r="693" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A693" s="11">
+        <v>17</v>
+      </c>
+      <c r="B693" s="11">
+        <v>2064869</v>
+      </c>
+      <c r="C693" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="D693" s="11">
+        <v>90787947</v>
+      </c>
+      <c r="E693" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F693" s="12">
+        <v>46221</v>
+      </c>
+      <c r="G693" s="13">
+        <v>54</v>
+      </c>
+      <c r="H693" s="13">
+        <v>8.1</v>
+      </c>
+      <c r="I693" s="13">
+        <v>45.9</v>
+      </c>
+      <c r="J693" s="14">
+        <f t="shared" si="22"/>
+        <v>42.66</v>
+      </c>
+      <c r="K693" s="14"/>
+      <c r="L693" s="14">
+        <f t="shared" si="23"/>
+        <v>42.66</v>
+      </c>
+      <c r="M693" s="14"/>
+      <c r="N693" s="14"/>
+    </row>
+    <row r="694" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A694" s="11">
+        <v>18</v>
+      </c>
+      <c r="B694" s="11">
+        <v>1833947</v>
+      </c>
+      <c r="C694" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D694" s="11">
+        <v>89682866</v>
+      </c>
+      <c r="E694" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F694" s="12">
+        <v>46221</v>
+      </c>
+      <c r="G694" s="13">
+        <v>59.99</v>
+      </c>
+      <c r="H694" s="13">
+        <v>11.997999999999999</v>
+      </c>
+      <c r="I694" s="13">
+        <v>47.991999999999997</v>
+      </c>
+      <c r="J694" s="14">
+        <f t="shared" si="22"/>
+        <v>44.392600000000002</v>
+      </c>
+      <c r="K694" s="14"/>
+      <c r="L694" s="14">
+        <f t="shared" si="23"/>
+        <v>44.392600000000002</v>
+      </c>
+      <c r="M694" s="14"/>
+      <c r="N694" s="14"/>
+    </row>
+    <row r="695" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A695" s="11">
+        <v>19</v>
+      </c>
+      <c r="B695" s="11">
+        <v>1833948</v>
+      </c>
+      <c r="C695" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D695" s="11">
+        <v>89682880</v>
+      </c>
+      <c r="E695" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F695" s="12">
+        <v>46221</v>
+      </c>
+      <c r="G695" s="13">
+        <v>55.35</v>
+      </c>
+      <c r="H695" s="13">
+        <v>11.07</v>
+      </c>
+      <c r="I695" s="13">
+        <v>44.28</v>
+      </c>
+      <c r="J695" s="14">
+        <f t="shared" si="22"/>
+        <v>40.958999999999996</v>
+      </c>
+      <c r="K695" s="14"/>
+      <c r="L695" s="14">
+        <f t="shared" si="23"/>
+        <v>40.958999999999996</v>
+      </c>
+      <c r="M695" s="14"/>
+      <c r="N695" s="14"/>
+    </row>
+    <row r="696" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A696" s="11">
+        <v>20</v>
+      </c>
+      <c r="B696" s="11">
+        <v>1904564</v>
+      </c>
+      <c r="C696" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D696" s="11">
+        <v>89682894</v>
+      </c>
+      <c r="E696" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F696" s="12">
+        <v>46221</v>
+      </c>
+      <c r="G696" s="13">
+        <v>34.08</v>
+      </c>
+      <c r="H696" s="13">
+        <v>6.8159999999999998</v>
+      </c>
+      <c r="I696" s="13">
+        <v>27.263999999999999</v>
+      </c>
+      <c r="J696" s="14">
+        <f t="shared" si="22"/>
+        <v>25.219199999999997</v>
+      </c>
+      <c r="K696" s="14"/>
+      <c r="L696" s="14">
+        <f t="shared" si="23"/>
+        <v>25.219199999999997</v>
+      </c>
+      <c r="M696" s="14"/>
+      <c r="N696" s="14"/>
+    </row>
+    <row r="697" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A697" s="11">
+        <v>21</v>
+      </c>
+      <c r="B697" s="11">
+        <v>2065066</v>
+      </c>
+      <c r="C697" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="D697" s="11">
+        <v>90787844</v>
+      </c>
+      <c r="E697" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F697" s="12">
+        <v>46222</v>
+      </c>
+      <c r="G697" s="13">
+        <v>55.34</v>
+      </c>
+      <c r="H697" s="13">
+        <v>8.3010000000000002</v>
+      </c>
+      <c r="I697" s="13">
+        <v>47.039000000000001</v>
+      </c>
+      <c r="J697" s="14">
+        <f t="shared" si="22"/>
+        <v>43.718599999999995</v>
+      </c>
+      <c r="K697" s="14"/>
+      <c r="L697" s="14">
+        <f t="shared" si="23"/>
+        <v>43.718599999999995</v>
+      </c>
+      <c r="M697" s="14"/>
+      <c r="N697" s="14"/>
+    </row>
+    <row r="698" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A698" s="11">
+        <v>22</v>
+      </c>
+      <c r="B698" s="11">
+        <v>2065067</v>
+      </c>
+      <c r="C698" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="D698" s="11">
+        <v>90787839</v>
+      </c>
+      <c r="E698" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F698" s="12">
+        <v>46222</v>
+      </c>
+      <c r="G698" s="13">
+        <v>51.42</v>
+      </c>
+      <c r="H698" s="13">
+        <v>7.7130000000000001</v>
+      </c>
+      <c r="I698" s="13">
+        <v>43.707000000000001</v>
+      </c>
+      <c r="J698" s="14">
+        <f t="shared" si="22"/>
+        <v>40.6218</v>
+      </c>
+      <c r="K698" s="14"/>
+      <c r="L698" s="14">
+        <f t="shared" si="23"/>
+        <v>40.6218</v>
+      </c>
+      <c r="M698" s="14"/>
+      <c r="N698" s="14"/>
+    </row>
+    <row r="699" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A699" s="11">
+        <v>23</v>
+      </c>
+      <c r="B699" s="11">
+        <v>2064887</v>
+      </c>
+      <c r="C699" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="D699" s="11">
+        <v>90790678</v>
+      </c>
+      <c r="E699" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F699" s="12">
+        <v>46222</v>
+      </c>
+      <c r="G699" s="13">
+        <v>42.2</v>
+      </c>
+      <c r="H699" s="13">
+        <v>6.33</v>
+      </c>
+      <c r="I699" s="13">
+        <v>35.869999999999997</v>
+      </c>
+      <c r="J699" s="14">
+        <f t="shared" si="22"/>
+        <v>33.338000000000001</v>
+      </c>
+      <c r="K699" s="14"/>
+      <c r="L699" s="14">
+        <f t="shared" si="23"/>
+        <v>33.338000000000001</v>
+      </c>
+      <c r="M699" s="14"/>
+      <c r="N699" s="14"/>
+    </row>
+    <row r="700" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A700" s="11">
+        <v>24</v>
+      </c>
+      <c r="B700" s="11">
+        <v>2059578</v>
+      </c>
+      <c r="C700" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="D700" s="11">
+        <v>88321647</v>
+      </c>
+      <c r="E700" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F700" s="12">
+        <v>46222</v>
+      </c>
+      <c r="G700" s="13">
+        <v>43.09</v>
+      </c>
+      <c r="H700" s="13">
+        <v>8.6180000000000003</v>
+      </c>
+      <c r="I700" s="13">
+        <v>34.472000000000001</v>
+      </c>
+      <c r="J700" s="14">
+        <f t="shared" si="22"/>
+        <v>31.886600000000001</v>
+      </c>
+      <c r="K700" s="14"/>
+      <c r="L700" s="14">
+        <f t="shared" si="23"/>
+        <v>31.886600000000001</v>
+      </c>
+      <c r="M700" s="14"/>
+      <c r="N700" s="14"/>
+    </row>
+    <row r="701" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A701" s="11">
+        <v>25</v>
+      </c>
+      <c r="B701" s="11">
+        <v>2064888</v>
+      </c>
+      <c r="C701" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D701" s="11">
+        <v>90787462</v>
+      </c>
+      <c r="E701" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F701" s="12">
+        <v>46224</v>
+      </c>
+      <c r="G701" s="13">
+        <v>59.46</v>
+      </c>
+      <c r="H701" s="13">
+        <v>8.9190000000000005</v>
+      </c>
+      <c r="I701" s="13">
+        <v>50.540999999999997</v>
+      </c>
+      <c r="J701" s="14">
+        <f t="shared" si="22"/>
+        <v>46.973399999999998</v>
+      </c>
+      <c r="K701" s="14"/>
+      <c r="L701" s="14">
+        <f t="shared" si="23"/>
+        <v>46.973399999999998</v>
+      </c>
+      <c r="M701" s="14"/>
+      <c r="N701" s="14"/>
+    </row>
+    <row r="702" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A702" s="11">
+        <v>26</v>
+      </c>
+      <c r="B702" s="11">
+        <v>2011712</v>
+      </c>
+      <c r="C702" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D702" s="11">
+        <v>88321378</v>
+      </c>
+      <c r="E702" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F702" s="12">
+        <v>46224</v>
+      </c>
+      <c r="G702" s="13">
+        <v>39.840000000000003</v>
+      </c>
+      <c r="H702" s="13">
+        <v>7.968</v>
+      </c>
+      <c r="I702" s="13">
+        <v>31.872</v>
+      </c>
+      <c r="J702" s="14">
+        <f t="shared" si="22"/>
+        <v>29.481600000000004</v>
+      </c>
+      <c r="K702" s="14"/>
+      <c r="L702" s="14">
+        <f t="shared" si="23"/>
+        <v>29.481600000000004</v>
+      </c>
+      <c r="M702" s="14"/>
+      <c r="N702" s="14"/>
+    </row>
+    <row r="703" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A703" s="11">
+        <v>27</v>
+      </c>
+      <c r="B703" s="11">
+        <v>1988586</v>
+      </c>
+      <c r="C703" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D703" s="11">
+        <v>90784668</v>
+      </c>
+      <c r="E703" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F703" s="12">
+        <v>46225</v>
+      </c>
+      <c r="G703" s="13">
+        <v>39</v>
+      </c>
+      <c r="H703" s="13">
+        <v>5.85</v>
+      </c>
+      <c r="I703" s="13">
+        <v>33.15</v>
+      </c>
+      <c r="J703" s="14">
+        <f t="shared" si="22"/>
+        <v>30.809999999999995</v>
+      </c>
+      <c r="K703" s="14"/>
+      <c r="L703" s="14">
+        <f t="shared" si="23"/>
+        <v>30.809999999999995</v>
+      </c>
+      <c r="M703" s="14"/>
+      <c r="N703" s="14"/>
+    </row>
+    <row r="704" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A704" s="11">
+        <v>28</v>
+      </c>
+      <c r="B704" s="11">
+        <v>1876018</v>
+      </c>
+      <c r="C704" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="D704" s="11">
+        <v>88579642</v>
+      </c>
+      <c r="E704" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F704" s="12">
+        <v>46226</v>
+      </c>
+      <c r="G704" s="13">
+        <v>48.84</v>
+      </c>
+      <c r="H704" s="13">
+        <v>9.7680000000000007</v>
+      </c>
+      <c r="I704" s="13">
+        <v>39.072000000000003</v>
+      </c>
+      <c r="J704" s="14">
+        <f t="shared" si="22"/>
+        <v>36.141599999999997</v>
+      </c>
+      <c r="K704" s="14"/>
+      <c r="L704" s="14">
+        <f t="shared" si="23"/>
+        <v>36.141599999999997</v>
+      </c>
+      <c r="M704" s="14"/>
+      <c r="N704" s="14"/>
+    </row>
+    <row r="705" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A705" s="11">
+        <v>29</v>
+      </c>
+      <c r="B705" s="11">
+        <v>2011610</v>
+      </c>
+      <c r="C705" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D705" s="11">
+        <v>88321542</v>
+      </c>
+      <c r="E705" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F705" s="12">
+        <v>46227</v>
+      </c>
+      <c r="G705" s="13">
+        <v>50.39</v>
+      </c>
+      <c r="H705" s="13">
+        <v>10.077999999999999</v>
+      </c>
+      <c r="I705" s="13">
+        <v>40.311999999999998</v>
+      </c>
+      <c r="J705" s="14">
+        <f t="shared" si="22"/>
+        <v>37.288600000000002</v>
+      </c>
+      <c r="K705" s="14"/>
+      <c r="L705" s="14">
+        <f t="shared" si="23"/>
+        <v>37.288600000000002</v>
+      </c>
+      <c r="M705" s="14"/>
+      <c r="N705" s="14"/>
+    </row>
+    <row r="706" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A706" s="11">
+        <v>30</v>
+      </c>
+      <c r="B706" s="11">
+        <v>2064795</v>
+      </c>
+      <c r="C706" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="D706" s="11">
+        <v>90789685</v>
+      </c>
+      <c r="E706" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F706" s="12">
+        <v>46228</v>
+      </c>
+      <c r="G706" s="13">
+        <v>14.79</v>
+      </c>
+      <c r="H706" s="13">
+        <v>2.218</v>
+      </c>
+      <c r="I706" s="13">
+        <v>12.571999999999999</v>
+      </c>
+      <c r="J706" s="14">
+        <f t="shared" si="22"/>
+        <v>11.684599999999998</v>
+      </c>
+      <c r="K706" s="14"/>
+      <c r="L706" s="14">
+        <f t="shared" si="23"/>
+        <v>11.684599999999998</v>
+      </c>
+      <c r="M706" s="14"/>
+      <c r="N706" s="14"/>
+    </row>
+    <row r="707" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A707" s="11">
+        <v>31</v>
+      </c>
+      <c r="B707" s="11">
+        <v>2058295</v>
+      </c>
+      <c r="C707" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D707" s="11">
+        <v>88321656</v>
+      </c>
+      <c r="E707" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F707" s="12">
+        <v>46229</v>
+      </c>
+      <c r="G707" s="13">
+        <v>13.5</v>
+      </c>
+      <c r="H707" s="13">
+        <v>2.7</v>
+      </c>
+      <c r="I707" s="13">
+        <v>10.8</v>
+      </c>
+      <c r="J707" s="14">
+        <f t="shared" si="22"/>
+        <v>9.9899999999999984</v>
+      </c>
+      <c r="K707" s="14"/>
+      <c r="L707" s="14">
+        <f t="shared" si="23"/>
+        <v>9.9899999999999984</v>
+      </c>
+      <c r="M707" s="14"/>
+      <c r="N707" s="14"/>
+    </row>
+    <row r="708" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A708" s="11">
+        <v>32</v>
+      </c>
+      <c r="B708" s="11">
+        <v>2049554</v>
+      </c>
+      <c r="C708" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D708" s="11">
+        <v>89884978</v>
+      </c>
+      <c r="E708" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F708" s="12">
+        <v>46231</v>
+      </c>
+      <c r="G708" s="13">
+        <v>41.41</v>
+      </c>
+      <c r="H708" s="13">
+        <v>4.141</v>
+      </c>
+      <c r="I708" s="13">
+        <v>37.268999999999998</v>
+      </c>
+      <c r="J708" s="14">
+        <f t="shared" si="22"/>
+        <v>34.784399999999998</v>
+      </c>
+      <c r="K708" s="14"/>
+      <c r="L708" s="14">
+        <f t="shared" si="23"/>
+        <v>34.784399999999998</v>
+      </c>
+      <c r="M708" s="14"/>
+      <c r="N708" s="14"/>
+    </row>
+    <row r="709" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A709" s="11">
+        <v>1</v>
+      </c>
+      <c r="B709" s="11">
+        <v>2064896</v>
+      </c>
+      <c r="C709" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="D709" s="11">
+        <v>90787482</v>
+      </c>
+      <c r="E709" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F709" s="12">
+        <v>46204</v>
+      </c>
+      <c r="G709" s="13">
+        <v>7.59</v>
+      </c>
+      <c r="H709" s="13">
+        <v>1.1379999999999999</v>
+      </c>
+      <c r="I709" s="13">
+        <v>6.452</v>
+      </c>
+      <c r="J709" s="14">
+        <f t="shared" ref="J709:J715" si="24">G709*0.94-H709</f>
+        <v>5.9965999999999999</v>
+      </c>
+      <c r="K709" s="14"/>
+      <c r="L709" s="14">
+        <f t="shared" ref="L709:L715" si="25">J709-K709</f>
+        <v>5.9965999999999999</v>
+      </c>
+      <c r="M709" s="14"/>
+      <c r="N709" s="14"/>
+    </row>
+    <row r="710" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A710" s="11">
+        <v>2</v>
+      </c>
+      <c r="B710" s="11">
+        <v>2065099</v>
+      </c>
+      <c r="C710" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="D710" s="11">
+        <v>90789921</v>
+      </c>
+      <c r="E710" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F710" s="12">
+        <v>46211</v>
+      </c>
+      <c r="G710" s="13">
+        <v>11.32</v>
+      </c>
+      <c r="H710" s="13">
+        <v>1.698</v>
+      </c>
+      <c r="I710" s="13">
+        <v>9.6219999999999999</v>
+      </c>
+      <c r="J710" s="14">
+        <f t="shared" si="24"/>
+        <v>8.9428000000000001</v>
+      </c>
+      <c r="K710" s="14"/>
+      <c r="L710" s="14">
+        <f t="shared" si="25"/>
+        <v>8.9428000000000001</v>
+      </c>
+      <c r="M710" s="14"/>
+      <c r="N710" s="14"/>
+    </row>
+    <row r="711" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A711" s="11">
+        <v>3</v>
+      </c>
+      <c r="B711" s="11">
+        <v>2065099</v>
+      </c>
+      <c r="C711" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="D711" s="11">
+        <v>90789921</v>
+      </c>
+      <c r="E711" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F711" s="12">
+        <v>46211</v>
+      </c>
+      <c r="G711" s="13">
+        <v>1.016</v>
+      </c>
+      <c r="H711" s="13">
+        <v>0.152</v>
+      </c>
+      <c r="I711" s="13">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="J711" s="14">
+        <f t="shared" si="24"/>
+        <v>0.80303999999999998</v>
+      </c>
+      <c r="K711" s="14"/>
+      <c r="L711" s="14">
+        <f t="shared" si="25"/>
+        <v>0.80303999999999998</v>
+      </c>
+      <c r="M711" s="14"/>
+      <c r="N711" s="14"/>
+    </row>
+    <row r="712" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A712" s="11">
+        <v>4</v>
+      </c>
+      <c r="B712" s="11">
+        <v>264837</v>
+      </c>
+      <c r="C712" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="D712" s="11">
+        <v>90789707</v>
+      </c>
+      <c r="E712" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F712" s="12">
+        <v>46216</v>
+      </c>
+      <c r="G712" s="13">
+        <v>12.17</v>
+      </c>
+      <c r="H712" s="13">
+        <v>1.825</v>
+      </c>
+      <c r="I712" s="13">
+        <v>10.345000000000001</v>
+      </c>
+      <c r="J712" s="14">
+        <f t="shared" si="24"/>
+        <v>9.6148000000000007</v>
+      </c>
+      <c r="K712" s="14"/>
+      <c r="L712" s="14">
+        <f t="shared" si="25"/>
+        <v>9.6148000000000007</v>
+      </c>
+      <c r="M712" s="14"/>
+      <c r="N712" s="14"/>
+    </row>
+    <row r="713" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A713" s="11">
+        <v>5</v>
+      </c>
+      <c r="B713" s="11">
+        <v>2065006</v>
+      </c>
+      <c r="C713" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="D713" s="11">
+        <v>90789797</v>
+      </c>
+      <c r="E713" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F713" s="12">
+        <v>46217</v>
+      </c>
+      <c r="G713" s="13">
+        <v>6.2380000000000004</v>
+      </c>
+      <c r="H713" s="13">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="I713" s="13">
+        <v>5.3019999999999996</v>
+      </c>
+      <c r="J713" s="14">
+        <f t="shared" si="24"/>
+        <v>4.9277199999999999</v>
+      </c>
+      <c r="K713" s="14"/>
+      <c r="L713" s="14">
+        <f t="shared" si="25"/>
+        <v>4.9277199999999999</v>
+      </c>
+      <c r="M713" s="14"/>
+      <c r="N713" s="14"/>
+    </row>
+    <row r="714" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A714" s="11">
+        <v>6</v>
+      </c>
+      <c r="B714" s="11">
+        <v>1963874</v>
+      </c>
+      <c r="C714" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D714" s="11">
+        <v>90173215</v>
+      </c>
+      <c r="E714" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F714" s="12">
+        <v>46218</v>
+      </c>
+      <c r="G714" s="13">
+        <v>28.632999999999999</v>
+      </c>
+      <c r="H714" s="13">
+        <v>0</v>
+      </c>
+      <c r="I714" s="13">
+        <v>28.632999999999999</v>
+      </c>
+      <c r="J714" s="14">
+        <f t="shared" si="24"/>
+        <v>26.915019999999998</v>
+      </c>
+      <c r="K714" s="14"/>
+      <c r="L714" s="14">
+        <f t="shared" si="25"/>
+        <v>26.915019999999998</v>
+      </c>
+      <c r="M714" s="14"/>
+      <c r="N714" s="14"/>
+    </row>
+    <row r="715" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A715" s="11">
+        <v>7</v>
+      </c>
+      <c r="B715" s="11">
+        <v>1988552</v>
+      </c>
+      <c r="C715" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="D715" s="11">
+        <v>90786035</v>
+      </c>
+      <c r="E715" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F715" s="12">
+        <v>46232</v>
+      </c>
+      <c r="G715" s="13">
+        <v>10.17</v>
+      </c>
+      <c r="H715" s="13">
+        <v>1.5249999999999999</v>
+      </c>
+      <c r="I715" s="13">
+        <v>8.6449999999999996</v>
+      </c>
+      <c r="J715" s="14">
+        <f t="shared" si="24"/>
+        <v>8.0347999999999988</v>
+      </c>
+      <c r="K715" s="14"/>
+      <c r="L715" s="14">
+        <f t="shared" si="25"/>
+        <v>8.0347999999999988</v>
+      </c>
+      <c r="M715" s="14"/>
+      <c r="N715" s="14"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/شركة الشرق العربي للتامين.xlsx
+++ b/شركة الشرق العربي للتامين.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436D2EE8-DD14-4808-A87A-4A78D30422F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F638024-7E1A-409F-8347-C87315D97C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="413">
   <si>
     <t>الرقم</t>
   </si>
@@ -1254,6 +1254,24 @@
   </si>
   <si>
     <t>ساجده علي العمرات</t>
+  </si>
+  <si>
+    <t>علي محمد علي اجخيدم العمرات</t>
+  </si>
+  <si>
+    <t>ايمن عيد محمد سلمان النوافلة</t>
+  </si>
+  <si>
+    <t>وجدان محمود النوافلة</t>
+  </si>
+  <si>
+    <t>ابراهيم سينان الرواجفة</t>
+  </si>
+  <si>
+    <t>خليل يوسف صقر المغاري</t>
+  </si>
+  <si>
+    <t>قاسم محمود الخليفات</t>
   </si>
 </sst>
 </file>
@@ -1678,8 +1696,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:N715" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:N715" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:N740" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:N740" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N676">
     <sortCondition ref="F1:F676"/>
   </sortState>
@@ -2024,7 +2042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N715"/>
+  <dimension ref="A1:N740"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -32788,6 +32806,1006 @@
       <c r="M715" s="14"/>
       <c r="N715" s="14"/>
     </row>
+    <row r="716" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A716" s="11">
+        <v>1</v>
+      </c>
+      <c r="B716" s="11">
+        <v>2011614</v>
+      </c>
+      <c r="C716" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D716" s="11">
+        <v>92309277</v>
+      </c>
+      <c r="E716" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F716" s="12">
+        <v>46237</v>
+      </c>
+      <c r="G716" s="13">
+        <v>18.75</v>
+      </c>
+      <c r="H716" s="13">
+        <v>3.75</v>
+      </c>
+      <c r="I716" s="13">
+        <v>15</v>
+      </c>
+      <c r="J716" s="14">
+        <f t="shared" ref="J716:J740" si="26">G716*0.94-H716</f>
+        <v>13.875</v>
+      </c>
+      <c r="K716" s="14"/>
+      <c r="L716" s="14">
+        <f t="shared" ref="L716:L740" si="27">J716-K716</f>
+        <v>13.875</v>
+      </c>
+      <c r="M716" s="14"/>
+      <c r="N716" s="14"/>
+    </row>
+    <row r="717" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A717" s="11">
+        <v>2</v>
+      </c>
+      <c r="B717" s="11">
+        <v>2011613</v>
+      </c>
+      <c r="C717" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D717" s="11">
+        <v>92309275</v>
+      </c>
+      <c r="E717" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F717" s="12">
+        <v>46237</v>
+      </c>
+      <c r="G717" s="13">
+        <v>35.97</v>
+      </c>
+      <c r="H717" s="13">
+        <v>7.194</v>
+      </c>
+      <c r="I717" s="13">
+        <v>28.776</v>
+      </c>
+      <c r="J717" s="14">
+        <f t="shared" si="26"/>
+        <v>26.617799999999999</v>
+      </c>
+      <c r="K717" s="14"/>
+      <c r="L717" s="14">
+        <f t="shared" si="27"/>
+        <v>26.617799999999999</v>
+      </c>
+      <c r="M717" s="14"/>
+      <c r="N717" s="14"/>
+    </row>
+    <row r="718" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A718" s="11">
+        <v>3</v>
+      </c>
+      <c r="B718" s="11">
+        <v>1988556</v>
+      </c>
+      <c r="C718" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="D718" s="11">
+        <v>90784278</v>
+      </c>
+      <c r="E718" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F718" s="12">
+        <v>46239</v>
+      </c>
+      <c r="G718" s="13">
+        <v>41.19</v>
+      </c>
+      <c r="H718" s="13">
+        <v>6.1779999999999999</v>
+      </c>
+      <c r="I718" s="13">
+        <v>35.012</v>
+      </c>
+      <c r="J718" s="14">
+        <f t="shared" si="26"/>
+        <v>32.540599999999998</v>
+      </c>
+      <c r="K718" s="14"/>
+      <c r="L718" s="14">
+        <f t="shared" si="27"/>
+        <v>32.540599999999998</v>
+      </c>
+      <c r="M718" s="14"/>
+      <c r="N718" s="14"/>
+    </row>
+    <row r="719" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A719" s="11">
+        <v>4</v>
+      </c>
+      <c r="B719" s="11">
+        <v>1988584</v>
+      </c>
+      <c r="C719" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D719" s="11">
+        <v>90784282</v>
+      </c>
+      <c r="E719" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F719" s="12">
+        <v>46242</v>
+      </c>
+      <c r="G719" s="13">
+        <v>52.47</v>
+      </c>
+      <c r="H719" s="13">
+        <v>7.87</v>
+      </c>
+      <c r="I719" s="13">
+        <v>44.6</v>
+      </c>
+      <c r="J719" s="14">
+        <f t="shared" si="26"/>
+        <v>41.451799999999999</v>
+      </c>
+      <c r="K719" s="14"/>
+      <c r="L719" s="14">
+        <f t="shared" si="27"/>
+        <v>41.451799999999999</v>
+      </c>
+      <c r="M719" s="14"/>
+      <c r="N719" s="14"/>
+    </row>
+    <row r="720" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A720" s="11">
+        <v>5</v>
+      </c>
+      <c r="B720" s="11">
+        <v>1988585</v>
+      </c>
+      <c r="C720" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D720" s="11">
+        <v>90784283</v>
+      </c>
+      <c r="E720" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F720" s="12">
+        <v>46242</v>
+      </c>
+      <c r="G720" s="13">
+        <v>24.35</v>
+      </c>
+      <c r="H720" s="13">
+        <v>3.6520000000000001</v>
+      </c>
+      <c r="I720" s="13">
+        <v>20.698</v>
+      </c>
+      <c r="J720" s="14">
+        <f t="shared" si="26"/>
+        <v>19.236999999999998</v>
+      </c>
+      <c r="K720" s="14"/>
+      <c r="L720" s="14">
+        <f t="shared" si="27"/>
+        <v>19.236999999999998</v>
+      </c>
+      <c r="M720" s="14"/>
+      <c r="N720" s="14"/>
+    </row>
+    <row r="721" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A721" s="11">
+        <v>6</v>
+      </c>
+      <c r="B721" s="11">
+        <v>2011677</v>
+      </c>
+      <c r="C721" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D721" s="11">
+        <v>92309357</v>
+      </c>
+      <c r="E721" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F721" s="12">
+        <v>46245</v>
+      </c>
+      <c r="G721" s="13">
+        <v>7.63</v>
+      </c>
+      <c r="H721" s="13">
+        <v>1.526</v>
+      </c>
+      <c r="I721" s="13">
+        <v>6.1040000000000001</v>
+      </c>
+      <c r="J721" s="14">
+        <f t="shared" si="26"/>
+        <v>5.6461999999999994</v>
+      </c>
+      <c r="K721" s="14"/>
+      <c r="L721" s="14">
+        <f t="shared" si="27"/>
+        <v>5.6461999999999994</v>
+      </c>
+      <c r="M721" s="14"/>
+      <c r="N721" s="14"/>
+    </row>
+    <row r="722" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A722" s="11">
+        <v>7</v>
+      </c>
+      <c r="B722" s="11">
+        <v>2065034</v>
+      </c>
+      <c r="C722" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="D722" s="11">
+        <v>90788016</v>
+      </c>
+      <c r="E722" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F722" s="12">
+        <v>46247</v>
+      </c>
+      <c r="G722" s="13">
+        <v>36.86</v>
+      </c>
+      <c r="H722" s="13">
+        <v>5.5289999999999999</v>
+      </c>
+      <c r="I722" s="13">
+        <v>31.331</v>
+      </c>
+      <c r="J722" s="14">
+        <f t="shared" si="26"/>
+        <v>29.119399999999995</v>
+      </c>
+      <c r="K722" s="14"/>
+      <c r="L722" s="14">
+        <f t="shared" si="27"/>
+        <v>29.119399999999995</v>
+      </c>
+      <c r="M722" s="14"/>
+      <c r="N722" s="14"/>
+    </row>
+    <row r="723" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A723" s="11">
+        <v>8</v>
+      </c>
+      <c r="B723" s="11">
+        <v>2064925</v>
+      </c>
+      <c r="C723" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="D723" s="11">
+        <v>90787526</v>
+      </c>
+      <c r="E723" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F723" s="12">
+        <v>46247</v>
+      </c>
+      <c r="G723" s="13">
+        <v>44.67</v>
+      </c>
+      <c r="H723" s="13">
+        <v>6.7</v>
+      </c>
+      <c r="I723" s="13">
+        <v>37.97</v>
+      </c>
+      <c r="J723" s="14">
+        <f t="shared" si="26"/>
+        <v>35.2898</v>
+      </c>
+      <c r="K723" s="14"/>
+      <c r="L723" s="14">
+        <f t="shared" si="27"/>
+        <v>35.2898</v>
+      </c>
+      <c r="M723" s="14"/>
+      <c r="N723" s="14"/>
+    </row>
+    <row r="724" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A724" s="11">
+        <v>9</v>
+      </c>
+      <c r="B724" s="11">
+        <v>2064927</v>
+      </c>
+      <c r="C724" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="D724" s="11">
+        <v>90787525</v>
+      </c>
+      <c r="E724" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F724" s="12">
+        <v>46247</v>
+      </c>
+      <c r="G724" s="13">
+        <v>41.4</v>
+      </c>
+      <c r="H724" s="13">
+        <v>6.21</v>
+      </c>
+      <c r="I724" s="13">
+        <v>35.19</v>
+      </c>
+      <c r="J724" s="14">
+        <f t="shared" si="26"/>
+        <v>32.705999999999996</v>
+      </c>
+      <c r="K724" s="14"/>
+      <c r="L724" s="14">
+        <f t="shared" si="27"/>
+        <v>32.705999999999996</v>
+      </c>
+      <c r="M724" s="14"/>
+      <c r="N724" s="14"/>
+    </row>
+    <row r="725" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A725" s="11">
+        <v>10</v>
+      </c>
+      <c r="B725" s="11">
+        <v>2064924</v>
+      </c>
+      <c r="C725" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D725" s="11">
+        <v>90790604</v>
+      </c>
+      <c r="E725" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F725" s="12">
+        <v>46250</v>
+      </c>
+      <c r="G725" s="13">
+        <v>25.38</v>
+      </c>
+      <c r="H725" s="13">
+        <v>3.8069999999999999</v>
+      </c>
+      <c r="I725" s="13">
+        <v>21.573</v>
+      </c>
+      <c r="J725" s="14">
+        <f t="shared" si="26"/>
+        <v>20.0502</v>
+      </c>
+      <c r="K725" s="14"/>
+      <c r="L725" s="14">
+        <f t="shared" si="27"/>
+        <v>20.0502</v>
+      </c>
+      <c r="M725" s="14"/>
+      <c r="N725" s="14"/>
+    </row>
+    <row r="726" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A726" s="11">
+        <v>11</v>
+      </c>
+      <c r="B726" s="11">
+        <v>1849233</v>
+      </c>
+      <c r="C726" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="D726" s="11">
+        <v>90828801</v>
+      </c>
+      <c r="E726" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F726" s="12">
+        <v>46250</v>
+      </c>
+      <c r="G726" s="13">
+        <v>38.65</v>
+      </c>
+      <c r="H726" s="13">
+        <v>7.73</v>
+      </c>
+      <c r="I726" s="13">
+        <v>30.92</v>
+      </c>
+      <c r="J726" s="14">
+        <f t="shared" si="26"/>
+        <v>28.600999999999996</v>
+      </c>
+      <c r="K726" s="14"/>
+      <c r="L726" s="14">
+        <f t="shared" si="27"/>
+        <v>28.600999999999996</v>
+      </c>
+      <c r="M726" s="14"/>
+      <c r="N726" s="14"/>
+    </row>
+    <row r="727" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A727" s="11">
+        <v>12</v>
+      </c>
+      <c r="B727" s="11">
+        <v>1948511</v>
+      </c>
+      <c r="C727" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D727" s="11">
+        <v>88672951</v>
+      </c>
+      <c r="E727" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F727" s="12">
+        <v>46251</v>
+      </c>
+      <c r="G727" s="13">
+        <v>69.63</v>
+      </c>
+      <c r="H727" s="13">
+        <v>13.926</v>
+      </c>
+      <c r="I727" s="13">
+        <v>55.704000000000001</v>
+      </c>
+      <c r="J727" s="14">
+        <f t="shared" si="26"/>
+        <v>51.526199999999989</v>
+      </c>
+      <c r="K727" s="14"/>
+      <c r="L727" s="14">
+        <f t="shared" si="27"/>
+        <v>51.526199999999989</v>
+      </c>
+      <c r="M727" s="14"/>
+      <c r="N727" s="14"/>
+    </row>
+    <row r="728" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A728" s="11">
+        <v>13</v>
+      </c>
+      <c r="B728" s="11">
+        <v>1904564</v>
+      </c>
+      <c r="C728" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D728" s="11">
+        <v>89682895</v>
+      </c>
+      <c r="E728" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F728" s="12">
+        <v>46251</v>
+      </c>
+      <c r="G728" s="13">
+        <v>35.950000000000003</v>
+      </c>
+      <c r="H728" s="13">
+        <v>7.19</v>
+      </c>
+      <c r="I728" s="13">
+        <v>28.76</v>
+      </c>
+      <c r="J728" s="14">
+        <f t="shared" si="26"/>
+        <v>26.602999999999998</v>
+      </c>
+      <c r="K728" s="14"/>
+      <c r="L728" s="14">
+        <f t="shared" si="27"/>
+        <v>26.602999999999998</v>
+      </c>
+      <c r="M728" s="14"/>
+      <c r="N728" s="14"/>
+    </row>
+    <row r="729" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A729" s="11">
+        <v>14</v>
+      </c>
+      <c r="B729" s="11">
+        <v>1833947</v>
+      </c>
+      <c r="C729" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D729" s="11">
+        <v>89682867</v>
+      </c>
+      <c r="E729" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F729" s="12">
+        <v>46251</v>
+      </c>
+      <c r="G729" s="13">
+        <v>48.22</v>
+      </c>
+      <c r="H729" s="13">
+        <v>9.6440000000000001</v>
+      </c>
+      <c r="I729" s="13">
+        <v>38.576000000000001</v>
+      </c>
+      <c r="J729" s="14">
+        <f t="shared" si="26"/>
+        <v>35.6828</v>
+      </c>
+      <c r="K729" s="14"/>
+      <c r="L729" s="14">
+        <f t="shared" si="27"/>
+        <v>35.6828</v>
+      </c>
+      <c r="M729" s="14"/>
+      <c r="N729" s="14"/>
+    </row>
+    <row r="730" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A730" s="11">
+        <v>15</v>
+      </c>
+      <c r="B730" s="11">
+        <v>1833948</v>
+      </c>
+      <c r="C730" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D730" s="11">
+        <v>89682881</v>
+      </c>
+      <c r="E730" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F730" s="12">
+        <v>46251</v>
+      </c>
+      <c r="G730" s="13">
+        <v>48.39</v>
+      </c>
+      <c r="H730" s="13">
+        <v>9.6780000000000008</v>
+      </c>
+      <c r="I730" s="13">
+        <v>38.712000000000003</v>
+      </c>
+      <c r="J730" s="14">
+        <f t="shared" si="26"/>
+        <v>35.808599999999998</v>
+      </c>
+      <c r="K730" s="14"/>
+      <c r="L730" s="14">
+        <f t="shared" si="27"/>
+        <v>35.808599999999998</v>
+      </c>
+      <c r="M730" s="14"/>
+      <c r="N730" s="14"/>
+    </row>
+    <row r="731" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A731" s="11">
+        <v>16</v>
+      </c>
+      <c r="B731" s="11">
+        <v>1988681</v>
+      </c>
+      <c r="C731" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D731" s="11">
+        <v>90786921</v>
+      </c>
+      <c r="E731" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F731" s="12">
+        <v>46252</v>
+      </c>
+      <c r="G731" s="13">
+        <v>26.37</v>
+      </c>
+      <c r="H731" s="13">
+        <v>3.9550000000000001</v>
+      </c>
+      <c r="I731" s="13">
+        <v>22.414999999999999</v>
+      </c>
+      <c r="J731" s="14">
+        <f t="shared" si="26"/>
+        <v>20.832799999999999</v>
+      </c>
+      <c r="K731" s="14"/>
+      <c r="L731" s="14">
+        <f t="shared" si="27"/>
+        <v>20.832799999999999</v>
+      </c>
+      <c r="M731" s="14"/>
+      <c r="N731" s="14"/>
+    </row>
+    <row r="732" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A732" s="11">
+        <v>17</v>
+      </c>
+      <c r="B732" s="11">
+        <v>2064976</v>
+      </c>
+      <c r="C732" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="D732" s="11">
+        <v>90790656</v>
+      </c>
+      <c r="E732" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F732" s="12">
+        <v>46255</v>
+      </c>
+      <c r="G732" s="13">
+        <v>12.62</v>
+      </c>
+      <c r="H732" s="13">
+        <v>1.893</v>
+      </c>
+      <c r="I732" s="13">
+        <v>10.727</v>
+      </c>
+      <c r="J732" s="14">
+        <f t="shared" si="26"/>
+        <v>9.9697999999999976</v>
+      </c>
+      <c r="K732" s="14"/>
+      <c r="L732" s="14">
+        <f t="shared" si="27"/>
+        <v>9.9697999999999976</v>
+      </c>
+      <c r="M732" s="14"/>
+      <c r="N732" s="14"/>
+    </row>
+    <row r="733" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A733" s="11">
+        <v>18</v>
+      </c>
+      <c r="B733" s="11">
+        <v>2064775</v>
+      </c>
+      <c r="C733" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="D733" s="11">
+        <v>90787279</v>
+      </c>
+      <c r="E733" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F733" s="12">
+        <v>46257</v>
+      </c>
+      <c r="G733" s="13">
+        <v>42.15</v>
+      </c>
+      <c r="H733" s="13">
+        <v>6.3220000000000001</v>
+      </c>
+      <c r="I733" s="13">
+        <v>35.828000000000003</v>
+      </c>
+      <c r="J733" s="14">
+        <f t="shared" si="26"/>
+        <v>33.298999999999992</v>
+      </c>
+      <c r="K733" s="14"/>
+      <c r="L733" s="14">
+        <f t="shared" si="27"/>
+        <v>33.298999999999992</v>
+      </c>
+      <c r="M733" s="14"/>
+      <c r="N733" s="14"/>
+    </row>
+    <row r="734" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A734" s="11">
+        <v>19</v>
+      </c>
+      <c r="B734" s="11">
+        <v>2064776</v>
+      </c>
+      <c r="C734" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="D734" s="11">
+        <v>90787272</v>
+      </c>
+      <c r="E734" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F734" s="12">
+        <v>46257</v>
+      </c>
+      <c r="G734" s="13">
+        <v>40.89</v>
+      </c>
+      <c r="H734" s="13">
+        <v>6.133</v>
+      </c>
+      <c r="I734" s="13">
+        <v>34.756999999999998</v>
+      </c>
+      <c r="J734" s="14">
+        <f t="shared" si="26"/>
+        <v>32.303599999999996</v>
+      </c>
+      <c r="K734" s="14"/>
+      <c r="L734" s="14">
+        <f t="shared" si="27"/>
+        <v>32.303599999999996</v>
+      </c>
+      <c r="M734" s="14"/>
+      <c r="N734" s="14"/>
+    </row>
+    <row r="735" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A735" s="11">
+        <v>20</v>
+      </c>
+      <c r="B735" s="11">
+        <v>2064774</v>
+      </c>
+      <c r="C735" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="D735" s="11">
+        <v>90790419</v>
+      </c>
+      <c r="E735" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F735" s="12">
+        <v>46257</v>
+      </c>
+      <c r="G735" s="13">
+        <v>43.09</v>
+      </c>
+      <c r="H735" s="13">
+        <v>6.4630000000000001</v>
+      </c>
+      <c r="I735" s="13">
+        <v>36.627000000000002</v>
+      </c>
+      <c r="J735" s="14">
+        <f t="shared" si="26"/>
+        <v>34.041600000000003</v>
+      </c>
+      <c r="K735" s="14"/>
+      <c r="L735" s="14">
+        <f t="shared" si="27"/>
+        <v>34.041600000000003</v>
+      </c>
+      <c r="M735" s="14"/>
+      <c r="N735" s="14"/>
+    </row>
+    <row r="736" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A736" s="11">
+        <v>21</v>
+      </c>
+      <c r="B736" s="11">
+        <v>1902625</v>
+      </c>
+      <c r="C736" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D736" s="11">
+        <v>89810988</v>
+      </c>
+      <c r="E736" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F736" s="12">
+        <v>46259</v>
+      </c>
+      <c r="G736" s="13">
+        <v>56.19</v>
+      </c>
+      <c r="H736" s="13">
+        <v>11.238</v>
+      </c>
+      <c r="I736" s="13">
+        <v>44.951999999999998</v>
+      </c>
+      <c r="J736" s="14">
+        <f t="shared" si="26"/>
+        <v>41.580599999999997</v>
+      </c>
+      <c r="K736" s="14"/>
+      <c r="L736" s="14">
+        <f t="shared" si="27"/>
+        <v>41.580599999999997</v>
+      </c>
+      <c r="M736" s="14"/>
+      <c r="N736" s="14"/>
+    </row>
+    <row r="737" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A737" s="11">
+        <v>22</v>
+      </c>
+      <c r="B737" s="11">
+        <v>1963874</v>
+      </c>
+      <c r="C737" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="D737" s="11">
+        <v>90173816</v>
+      </c>
+      <c r="E737" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F737" s="12">
+        <v>46259</v>
+      </c>
+      <c r="G737" s="13">
+        <v>92.82</v>
+      </c>
+      <c r="H737" s="13">
+        <v>0</v>
+      </c>
+      <c r="I737" s="13">
+        <v>92.82</v>
+      </c>
+      <c r="J737" s="14">
+        <f t="shared" si="26"/>
+        <v>87.250799999999984</v>
+      </c>
+      <c r="K737" s="14"/>
+      <c r="L737" s="14">
+        <f t="shared" si="27"/>
+        <v>87.250799999999984</v>
+      </c>
+      <c r="M737" s="14"/>
+      <c r="N737" s="14"/>
+    </row>
+    <row r="738" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A738" s="11">
+        <v>23</v>
+      </c>
+      <c r="B738" s="11">
+        <v>20116448</v>
+      </c>
+      <c r="C738" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="D738" s="11">
+        <v>92309319</v>
+      </c>
+      <c r="E738" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F738" s="12">
+        <v>46261</v>
+      </c>
+      <c r="G738" s="13">
+        <v>44.82</v>
+      </c>
+      <c r="H738" s="13">
+        <v>8.9640000000000004</v>
+      </c>
+      <c r="I738" s="13">
+        <v>35.856000000000002</v>
+      </c>
+      <c r="J738" s="14">
+        <f t="shared" si="26"/>
+        <v>33.166800000000002</v>
+      </c>
+      <c r="K738" s="14"/>
+      <c r="L738" s="14">
+        <f t="shared" si="27"/>
+        <v>33.166800000000002</v>
+      </c>
+      <c r="M738" s="14"/>
+      <c r="N738" s="14"/>
+    </row>
+    <row r="739" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A739" s="11">
+        <v>24</v>
+      </c>
+      <c r="B739" s="11">
+        <v>2011647</v>
+      </c>
+      <c r="C739" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D739" s="11">
+        <v>92309317</v>
+      </c>
+      <c r="E739" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F739" s="12">
+        <v>46261</v>
+      </c>
+      <c r="G739" s="13">
+        <v>42.12</v>
+      </c>
+      <c r="H739" s="13">
+        <v>8.4239999999999995</v>
+      </c>
+      <c r="I739" s="13">
+        <v>33.695999999999998</v>
+      </c>
+      <c r="J739" s="14">
+        <f t="shared" si="26"/>
+        <v>31.168799999999997</v>
+      </c>
+      <c r="K739" s="14"/>
+      <c r="L739" s="14">
+        <f t="shared" si="27"/>
+        <v>31.168799999999997</v>
+      </c>
+      <c r="M739" s="14"/>
+      <c r="N739" s="14"/>
+    </row>
+    <row r="740" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A740" s="11">
+        <v>25</v>
+      </c>
+      <c r="B740" s="11">
+        <v>2032859</v>
+      </c>
+      <c r="C740" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="D740" s="11">
+        <v>88914797</v>
+      </c>
+      <c r="E740" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F740" s="12">
+        <v>46265</v>
+      </c>
+      <c r="G740" s="13">
+        <v>27.93</v>
+      </c>
+      <c r="H740" s="13">
+        <v>2.7930000000000001</v>
+      </c>
+      <c r="I740" s="13">
+        <v>25.137</v>
+      </c>
+      <c r="J740" s="14">
+        <f t="shared" si="26"/>
+        <v>23.461199999999998</v>
+      </c>
+      <c r="K740" s="14"/>
+      <c r="L740" s="14">
+        <f t="shared" si="27"/>
+        <v>23.461199999999998</v>
+      </c>
+      <c r="M740" s="14"/>
+      <c r="N740" s="14"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
